--- a/data/trans_camb/IMC_inf_MED_R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R3-Provincia-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.7286414561373855</v>
+        <v>-1.513987077449402</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-17.74173439560144</v>
+        <v>-16.09308046196718</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2.18650375861725</v>
+        <v>-3.07679382678327</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-16.55216043705128</v>
+        <v>-14.37864274275527</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.228243978406246</v>
+        <v>-2.369912514974373</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-17.14921386963631</v>
+        <v>-15.31239492834094</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-16.51628179311019</v>
+        <v>-15.33271964177823</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-32.66197248048562</v>
+        <v>-30.16174675903193</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-14.42726253166327</v>
+        <v>-15.65971624202313</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-30.11603736227919</v>
+        <v>-24.77432631119823</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-12.0382813891922</v>
+        <v>-11.48093022939112</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-26.76257531286831</v>
+        <v>-24.46996279598769</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>17.50213966504111</v>
+        <v>13.00195725891025</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-2.657386641876603</v>
+        <v>-1.477721562555818</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>20.24083857101048</v>
+        <v>9.288665562802793</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-2.292762574192664</v>
+        <v>-1.22892810903407</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>13.20093420493196</v>
+        <v>7.135394298847608</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-5.763052296618822</v>
+        <v>-5.251951140273465</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.02584393886254248</v>
+        <v>-0.05703420534662335</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.6292756130923975</v>
+        <v>-0.6062509181213556</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.09972516790968015</v>
+        <v>-0.1557730085343551</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.7549344346413516</v>
+        <v>-0.7279670217686748</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.04864508681368595</v>
+        <v>-0.1012252471431386</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.6792013737835746</v>
+        <v>-0.6540329869482182</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.4822369553329033</v>
+        <v>-0.4665755214636688</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.9105443006967372</v>
+        <v>-0.9040642357960614</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.5030873257961538</v>
+        <v>-0.5949236259073556</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>-1</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.3861773225997169</v>
+        <v>-0.4161186513032628</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.8776630510805251</v>
+        <v>-0.8537507749524752</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.9617999942688669</v>
+        <v>0.7716147590098927</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-0.05020382982042784</v>
+        <v>0.047850977750166</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1.591857923947971</v>
+        <v>0.7497385961799294</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3056704370040967</v>
+        <v>0.1247786581715378</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.6805288411955981</v>
+        <v>0.3836580802256384</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.25549058740418</v>
+        <v>-0.2228653528154005</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-0.7171552430615458</v>
+        <v>-1.329911850316867</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-14.19132838684621</v>
+        <v>-12.6233421954974</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-9.129489486398212</v>
+        <v>-11.42102303871315</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-12.42473979739195</v>
+        <v>-13.11232139968739</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-4.933403517615489</v>
+        <v>-6.099628139248425</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-13.34789468481835</v>
+        <v>-12.84730272879214</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-13.32848285141336</v>
+        <v>-11.96247517640241</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-27.34672121036036</v>
+        <v>-24.51288764522587</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-20.53765878477067</v>
+        <v>-21.23092780650082</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-24.26374181029683</v>
+        <v>-25.13065779387259</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-12.14328461611289</v>
+        <v>-13.25933544251156</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-21.99753316341321</v>
+        <v>-21.50618982508291</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10.53788790970935</v>
+        <v>9.015796181520344</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2.229823903551104</v>
+        <v>2.627529690094418</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.9418966697865698</v>
+        <v>-1.730580168950296</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>2.34652392613209</v>
+        <v>1.499143273664784</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>3.236968922517009</v>
+        <v>1.190905333631895</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-2.992263558765033</v>
+        <v>-2.908867118220119</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.02354269833896422</v>
+        <v>-0.04662241433281802</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.4658714643351322</v>
+        <v>-0.4425336084968339</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.3414353742921818</v>
+        <v>-0.4164283888504869</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.4646750170999046</v>
+        <v>-0.4780957761886122</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.1719764619202789</v>
+        <v>-0.217829350440757</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.4653022388667435</v>
+        <v>-0.4588016751908714</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.3654751477286743</v>
+        <v>-0.3528808671969612</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.7741302254426047</v>
+        <v>-0.7572202258986174</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.6347871195935665</v>
+        <v>-0.643129449282796</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.7858380331485935</v>
+        <v>-0.773494107028152</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.3929783971121439</v>
+        <v>-0.4219281289916387</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.6972221992597485</v>
+        <v>-0.7053607834259384</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.4229077809691884</v>
+        <v>0.4111038796824482</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.157394041073018</v>
+        <v>0.1425995109585891</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.06577990094798776</v>
+        <v>-0.02936500408209416</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.1579603582320996</v>
+        <v>0.0803282923356797</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.1378099039478165</v>
+        <v>0.0463982677473123</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.1092757588984154</v>
+        <v>-0.1007102381524305</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2.157373834126566</v>
+        <v>1.673289293436572</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>13.29819505966123</v>
+        <v>12.23303608990363</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-9.471561065189027</v>
+        <v>-8.270055182910244</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-2.790946436909539</v>
+        <v>-2.350263077771888</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-3.506256314512049</v>
+        <v>-3.099009054637339</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>5.335877112626447</v>
+        <v>5.20203679196867</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-11.12715122054658</v>
+        <v>-10.70415909534179</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-3.373985176488689</v>
+        <v>-2.916113372193673</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-20.48167001146365</v>
+        <v>-18.98258089903326</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-17.02607862314759</v>
+        <v>-15.05572554605176</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-12.1915896979958</v>
+        <v>-10.68076369694569</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-6.437473313221738</v>
+        <v>-4.850201343697333</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>16.09496545819059</v>
+        <v>12.23405896021737</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>32.42052568273098</v>
+        <v>30.3856047983283</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1.910543406454489</v>
+        <v>2.219810356079518</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>13.13150149079573</v>
+        <v>13.31314095955245</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>4.797037178287449</v>
+        <v>4.612946856885984</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>18.16869030095991</v>
+        <v>17.86346553267141</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.1094975043098076</v>
+        <v>0.08603110842259114</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.6749498616439102</v>
+        <v>0.6289537967619</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.5043424930959947</v>
+        <v>-0.4738197491161185</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.1486125544036968</v>
+        <v>-0.1346546107900183</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.182153287817262</v>
+        <v>-0.1678278348935257</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.2772037958066531</v>
+        <v>0.2817179803092676</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.4229773214302027</v>
+        <v>-0.4241601111450476</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.1964747052514165</v>
+        <v>-0.1418258008356922</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.8056345911766092</v>
+        <v>-0.8028092569777248</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.706818393732103</v>
+        <v>-0.7055106918414262</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.4947892057361577</v>
+        <v>-0.4752150409995677</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.3110251819476945</v>
+        <v>-0.2411391126153915</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1.194390090669214</v>
+        <v>0.9584113708700637</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2.207899041517752</v>
+        <v>2.136458987625837</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.2219655890835049</v>
+        <v>0.2864225407058065</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1.053801109822216</v>
+        <v>1.048174575132235</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.3219296382423421</v>
+        <v>0.3360142227741266</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.160539103583117</v>
+        <v>1.200019261237674</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-0.5575806099646086</v>
+        <v>-0.383736893705533</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-17.28454427672995</v>
+        <v>-16.74376731694182</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1.232657132873141</v>
+        <v>-0.7610205795043055</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-9.131238675911691</v>
+        <v>-7.972606604232775</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.7608187259872057</v>
+        <v>-0.425135632803389</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-14.09156660773438</v>
+        <v>-12.88425924947996</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-15.54159628056647</v>
+        <v>-13.49197629426894</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-32.07781692529225</v>
+        <v>-29.52047246419984</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-11.10788864386035</v>
+        <v>-12.63480967438754</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-19.48990829078019</v>
+        <v>-16.97591559681193</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-9.460979261575835</v>
+        <v>-9.262308474956548</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-23.48015855282875</v>
+        <v>-21.68989761610317</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>15.51052032618682</v>
+        <v>13.39803113537963</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>8.828996685740229</v>
+        <v>5.57093112545262</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>15.42870638429021</v>
+        <v>8.709729728314068</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>6.668179317028628</v>
+        <v>8.418887439584681</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>12.30038239197906</v>
+        <v>9.310194540874246</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-0.1539076590808447</v>
+        <v>-0.4859248840541525</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.01952610931178701</v>
+        <v>-0.01493784337032878</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.6052934677432089</v>
+        <v>-0.6517897489461558</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.08736561801547849</v>
+        <v>-0.05937132668565055</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.6471842728143004</v>
+        <v>-0.6219861117874032</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.0351438424724128</v>
+        <v>-0.02167357823749073</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.6509195687962831</v>
+        <v>-0.6568444969769458</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.4454380668737785</v>
+        <v>-0.4268915447665232</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>-1</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.5850422701288837</v>
+        <v>-0.6612037178257693</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>-1</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.3697841913048533</v>
+        <v>-0.4038058069344446</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.9319456219027638</v>
+        <v>-0.9375101014219434</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.7432912147262831</v>
+        <v>0.6993601194508349</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.7475484928175</v>
+        <v>0.5978236867625327</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1.994930513084003</v>
+        <v>1.086040924663001</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.470175742878039</v>
+        <v>1.948506082970874</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.7566820376507126</v>
+        <v>0.6417256813887011</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.1159576810426138</v>
+        <v>0.07206590303938219</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-12.68643666307322</v>
+        <v>-6.143270293061925</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-5.452977434217451</v>
+        <v>-0.4879469497479388</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-7.256559013693341</v>
+        <v>-9.25736304375229</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>6.860708428018644</v>
+        <v>7.507479635334258</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-10.15168414073469</v>
+        <v>-7.653663749639215</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.3201600798977106</v>
+        <v>3.295760619697305</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-30.70348861470365</v>
+        <v>-19.95310310327121</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-23.44403667475984</v>
+        <v>-15.3717432715447</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-22.44710104823672</v>
+        <v>-23.26353030414411</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-11.82951961248565</v>
+        <v>-7.971742138859785</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-21.3258132766389</v>
+        <v>-17.5029962875097</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-13.76654360882288</v>
+        <v>-8.388385193649714</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>2.69454194792405</v>
+        <v>7.994308827400616</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>9.999770445002781</v>
+        <v>14.72546063100044</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>6.865629084413549</v>
+        <v>1.989982751761803</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>23.67436463345184</v>
+        <v>23.68458397467228</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>2.038292851216926</v>
+        <v>1.569457783551729</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>11.90946298514101</v>
+        <v>15.11460462956665</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.4792596073065248</v>
+        <v>-0.3037603883976838</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.2059988863051887</v>
+        <v>-0.02412704437574466</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.4153057415186635</v>
+        <v>-0.5166382392514099</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.392650510478166</v>
+        <v>0.4189801179540619</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.4565922586725395</v>
+        <v>-0.4016762191603461</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.01439983868594802</v>
+        <v>0.172966661233318</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.802002449401767</v>
+        <v>-0.7368860485955784</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.6489615149130634</v>
+        <v>-0.6201889583634093</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.8264111339978627</v>
+        <v>-0.8873870029104816</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.4525235292827273</v>
+        <v>-0.3354796703366253</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.7388401852391655</v>
+        <v>-0.7336954922294195</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.4405498161132163</v>
+        <v>-0.3497467448100729</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0.2290648011202933</v>
+        <v>0.7649276676496097</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.5850057712619577</v>
+        <v>1.225817854872622</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>1.443805238124064</v>
+        <v>0.3710496526848254</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>2.94964618658672</v>
+        <v>2.716794400016167</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.1817986837408594</v>
+        <v>0.1512131208646913</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.7682546212590349</v>
+        <v>1.098303147134913</v>
       </c>
     </row>
     <row r="34">
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>8.411137259126052</v>
+        <v>10.14875582157989</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>5.532294569427237</v>
+        <v>3.643818578640182</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-4.000783742542295</v>
+        <v>-6.146751153434352</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-9.31488029263077</v>
+        <v>-8.342343913422511</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>2.490825729845489</v>
+        <v>2.19069288424179</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>-0.2157021254156094</v>
+        <v>-1.222259855300365</v>
       </c>
     </row>
     <row r="35">
@@ -1427,22 +1427,22 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>-7.704859387141538</v>
+        <v>-3.346346416377988</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>-10.28187049740227</v>
+        <v>-11.76287655764033</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-14.83412958977931</v>
+        <v>-17.84760324526899</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-19.01448545667471</v>
+        <v>-20.17226290525156</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-7.740547846295878</v>
+        <v>-6.988478788482803</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-10.56260887146337</v>
+        <v>-10.982001581088</v>
       </c>
     </row>
     <row r="36">
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>21.7559095740244</v>
+        <v>24.22213016090501</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>22.00550211813133</v>
+        <v>20.23886334361282</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>5.527277922576138</v>
+        <v>4.152524840101178</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>2.754667579099929</v>
+        <v>4.223019560953264</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>11.12189253953506</v>
+        <v>11.21743541405422</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>10.90325990419738</v>
+        <v>10.05843170572511</v>
       </c>
     </row>
     <row r="37">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.4955455265449404</v>
+        <v>0.6035272114908288</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.3259373543612088</v>
+        <v>0.2166909623807302</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>-0.306852725260237</v>
+        <v>-0.4125126148809999</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.7144341177137267</v>
+        <v>-0.5598603255704855</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.1665980734305081</v>
+        <v>0.1379679264764454</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.01442716690233303</v>
+        <v>-0.07697685926868568</v>
       </c>
     </row>
     <row r="38">
@@ -1505,22 +1505,22 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>-0.3260586745617073</v>
+        <v>-0.1533930334713327</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>-0.5161887119854863</v>
+        <v>-0.5322325245039468</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-0.7906747601855934</v>
+        <v>-0.8090864714179239</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>-1</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.3980846127018909</v>
+        <v>-0.3541677621428411</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.5712187166060707</v>
+        <v>-0.5758091605032644</v>
       </c>
     </row>
     <row r="39">
@@ -1531,22 +1531,22 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>2.134916942610592</v>
+        <v>2.513121865213641</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>1.997613539932615</v>
+        <v>2.347808052458319</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.8749419342196283</v>
+        <v>0.63417808750603</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1.42623501811728</v>
+        <v>0.8976848420026419</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1.004651418606834</v>
+        <v>0.9989158332991199</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1.031559703931079</v>
+        <v>0.8597113294084296</v>
       </c>
     </row>
     <row r="40">
@@ -1561,22 +1561,22 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>-10.58115603106972</v>
+        <v>-9.632682292492245</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>4.049898556191883</v>
+        <v>5.774370125764025</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-4.113101310929763</v>
+        <v>-4.649023502632489</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>2.419533486998712</v>
+        <v>2.228403838194914</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-7.285360856761186</v>
+        <v>-7.165151660641003</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>4.134747130206754</v>
+        <v>4.676363949004586</v>
       </c>
     </row>
     <row r="41">
@@ -1587,22 +1587,22 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>-18.76140249807624</v>
+        <v>-17.23058734021902</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>-8.056073097809373</v>
+        <v>-4.266739017053</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-12.04069118732259</v>
+        <v>-12.02547726027841</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-6.974084524174653</v>
+        <v>-7.697274643413403</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-13.89331982884447</v>
+        <v>-12.82249154766398</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>-4.295279457151277</v>
+        <v>-3.658163003199426</v>
       </c>
     </row>
     <row r="42">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>-1.371720680766414</v>
+        <v>-1.449054994814119</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>16.4176684536945</v>
+        <v>18.17646645368666</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>3.393139406090925</v>
+        <v>2.562684468524181</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>14.46864869845435</v>
+        <v>14.39745423909127</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-1.746710188749346</v>
+        <v>-1.940906227730306</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>13.28356481355416</v>
+        <v>13.59542505200291</v>
       </c>
     </row>
     <row r="43">
@@ -1639,22 +1639,22 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>-0.4198013136894591</v>
+        <v>-0.4291478611856231</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.160677408896173</v>
+        <v>0.2572553016823984</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-0.2569549275582152</v>
+        <v>-0.2792359150941478</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.1511538386434475</v>
+        <v>0.1338453945447516</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.3532781143651259</v>
+        <v>-0.3657373233578114</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.2005001122463877</v>
+        <v>0.23869987890848</v>
       </c>
     </row>
     <row r="44">
@@ -1665,22 +1665,22 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>-0.6364649682018272</v>
+        <v>-0.6419417220613811</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>-0.2695909026515243</v>
+        <v>-0.1773496822456723</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-0.5979625815156486</v>
+        <v>-0.5851645202518897</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-0.3889152189808058</v>
+        <v>-0.4123506480586591</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.5660951522423654</v>
+        <v>-0.5661423116160454</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.1982958637486462</v>
+        <v>-0.1609808182000788</v>
       </c>
     </row>
     <row r="45">
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>-0.04159275105274747</v>
+        <v>-0.05015101072011993</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.8096504544785699</v>
+        <v>1.022685535739257</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0.2933155768885215</v>
+        <v>0.2380255910051503</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.273912236591985</v>
+        <v>1.236338247850863</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.0785957916432658</v>
+        <v>-0.1064750153613795</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.7207344617514272</v>
+        <v>0.8310827693025726</v>
       </c>
     </row>
     <row r="46">
@@ -1721,22 +1721,22 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>-18.10716010720984</v>
+        <v>-16.86816275183195</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>-22.38876570786628</v>
+        <v>-20.24461989222757</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-17.55589128734366</v>
+        <v>-14.55252504850279</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-28.52315120904332</v>
+        <v>-25.09834210729698</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-17.81114314416256</v>
+        <v>-15.64946626314857</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>-24.45215913826661</v>
+        <v>-21.78331144282291</v>
       </c>
     </row>
     <row r="47">
@@ -1747,22 +1747,22 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>-27.28547906729587</v>
+        <v>-26.07723561756447</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>-32.2111008481578</v>
+        <v>-29.30290331537729</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>-25.9463755692566</v>
+        <v>-21.80761662603524</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>-36.54109924423608</v>
+        <v>-31.99811489200655</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-24.01272956097448</v>
+        <v>-21.4242202795118</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>-30.98653122529649</v>
+        <v>-28.05486847512521</v>
       </c>
     </row>
     <row r="48">
@@ -1773,22 +1773,22 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>-8.767279776777478</v>
+        <v>-9.162748467346029</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>-12.41817077722338</v>
+        <v>-10.2872198598191</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-9.198761852412272</v>
+        <v>-7.270763899422969</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-20.84588777087379</v>
+        <v>-17.8463553068675</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-11.11771749475336</v>
+        <v>-9.740908527560507</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>-16.77515444486923</v>
+        <v>-15.43194820767612</v>
       </c>
     </row>
     <row r="49">
@@ -1799,22 +1799,22 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>-0.4950967336008837</v>
+        <v>-0.4947940256823819</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>-0.6121669386966124</v>
+        <v>-0.5938356845529624</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>-0.5353626265553599</v>
+        <v>-0.5013555613868843</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>-0.8698065452203896</v>
+        <v>-0.8646742304270115</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-0.5131713501599152</v>
+        <v>-0.4958848834968294</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-0.7045110702746736</v>
+        <v>-0.690248132131894</v>
       </c>
     </row>
     <row r="50">
@@ -1825,22 +1825,22 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>-0.6510256054514666</v>
+        <v>-0.6587212410114519</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>-0.7937135691730219</v>
+        <v>-0.7818653004861795</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-0.6954432323057039</v>
+        <v>-0.6748442596304688</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>-0.9538091242334052</v>
+        <v>-0.9527381804565069</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-0.6280361822863461</v>
+        <v>-0.6121935845528977</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-0.8187303899374579</v>
+        <v>-0.8205383038557094</v>
       </c>
     </row>
     <row r="51">
@@ -1851,22 +1851,22 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>-0.2738344580170435</v>
+        <v>-0.3043637015832736</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>-0.3669654253451906</v>
+        <v>-0.3200161318401943</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>-0.3056193368506243</v>
+        <v>-0.2902016352461338</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>-0.6968331059892239</v>
+        <v>-0.6985285406171421</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-0.3602311716606713</v>
+        <v>-0.3386571919397218</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-0.5246718975927795</v>
+        <v>-0.5128216493927141</v>
       </c>
     </row>
     <row r="52">
@@ -1881,22 +1881,22 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>-6.598248158520778</v>
+        <v>-5.583151166360387</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>-8.113762417935517</v>
+        <v>-6.68556263533474</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>-7.893069262130526</v>
+        <v>-8.197869741194271</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>-10.11183936014612</v>
+        <v>-9.143744298366643</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-7.176371486902122</v>
+        <v>-6.782909945409507</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>-8.722738741024012</v>
+        <v>-7.573650100786969</v>
       </c>
     </row>
     <row r="53">
@@ -1907,22 +1907,22 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>-11.03258844248462</v>
+        <v>-9.284304315577327</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>-12.91320251250455</v>
+        <v>-11.84553850774274</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>-11.27482969603891</v>
+        <v>-11.71637426954293</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>-14.10600311865373</v>
+        <v>-12.98082423588392</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-9.892999748091762</v>
+        <v>-9.331034448888031</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>-12.1826609401635</v>
+        <v>-10.70824123917432</v>
       </c>
     </row>
     <row r="54">
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>-2.142384736099197</v>
+        <v>-1.727670538408725</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>-2.543874511370215</v>
+        <v>-1.845889933489961</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>-3.426379899764664</v>
+        <v>-4.734638920651528</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-4.807337501895701</v>
+        <v>-4.459975793351885</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-3.951096404486645</v>
+        <v>-4.039963180515583</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>-5.004738583199533</v>
+        <v>-4.243707485344875</v>
       </c>
     </row>
     <row r="55">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>-0.2350514343468103</v>
+        <v>-0.2159870972607307</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>-0.2890390674109686</v>
+        <v>-0.2586344564447968</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>-0.3618655677473216</v>
+        <v>-0.3899495765883395</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>-0.4635872775860201</v>
+        <v>-0.4349421654826973</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-0.2869308769885928</v>
+        <v>-0.2886984772911741</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-0.3487588513599657</v>
+        <v>-0.3223544568969415</v>
       </c>
     </row>
     <row r="56">
@@ -1985,22 +1985,22 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>-0.354259004094362</v>
+        <v>-0.3396624314896944</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>-0.4393574037103257</v>
+        <v>-0.4281998567625147</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>-0.4813608701542939</v>
+        <v>-0.5075838240134847</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>-0.6060895617186332</v>
+        <v>-0.5883578104932133</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-0.3768725029847597</v>
+        <v>-0.3794695429892992</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>-0.4610866861073419</v>
+        <v>-0.4351962147731114</v>
       </c>
     </row>
     <row r="57">
@@ -2011,22 +2011,22 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>-0.07647618632731647</v>
+        <v>-0.07210510242710264</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>-0.09703842434576994</v>
+        <v>-0.07156923439645424</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>-0.1825640570666804</v>
+        <v>-0.2474241005013212</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>-0.2439439414312926</v>
+        <v>-0.2333212092101253</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-0.1701161162912276</v>
+        <v>-0.1806509855487162</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>-0.2107793357035836</v>
+        <v>-0.1880863014103842</v>
       </c>
     </row>
     <row r="58">
